--- a/Rekap_Pareto_LMO_Lengkap.xlsx
+++ b/Rekap_Pareto_LMO_Lengkap.xlsx
@@ -1101,7 +1101,7 @@
       <c r="D9" s="45" t="inlineStr">
         <is>
           <t>5. Overburden Removal
-Proses tidak dipadankan: dasar GWP HULU PROC dan LCI berbeda</t>
+5. Overburden Removal</t>
         </is>
       </c>
       <c r="E9" s="46" t="inlineStr">
@@ -3476,7 +3476,9 @@
           <t>Ammonium nitrate {RoW}| market for ammonium nitrate | Cut-off, S</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>1.3259296</v>
+      </c>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
@@ -3510,7 +3512,9 @@
     <row r="11" ht="21" customHeight="1">
       <c r="B11" s="39" t="n"/>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>0.07160300752919138</v>
+      </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
@@ -3704,9 +3708,7 @@
           <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>6.1744842</v>
-      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n">
@@ -3746,9 +3748,7 @@
     <row r="19" ht="21" customHeight="1">
       <c r="B19" s="39" t="n"/>
       <c r="C19" s="40" t="n"/>
-      <c r="D19" s="3" t="n">
-        <v>0.2551598752517306</v>
-      </c>
+      <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n">
@@ -3901,7 +3901,7 @@
       <c r="B23" s="40" t="n"/>
       <c r="C23" s="40" t="n"/>
       <c r="D23" s="3" t="n">
-        <v>0.5969395117679234</v>
+        <v>0.7800625474138602</v>
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n">
@@ -12009,7 +12009,7 @@
     <row r="1">
       <c r="A1" s="54" t="inlineStr">
         <is>
-          <t>AUDIT PARETO — LMO / LIMA SHEET</t>
+          <t>AUDIT PARETO — LMO / TUJUH SHEET</t>
         </is>
       </c>
     </row>
@@ -14680,14 +14680,14 @@
         </is>
       </c>
       <c r="H62" s="63" t="n">
-        <v>0.5969395117679234</v>
+        <v>0.7800625474138602</v>
       </c>
       <c r="I62" s="63" t="n">
-        <v>0.5969395117679234</v>
+        <v>0.7800625474138602</v>
       </c>
       <c r="J62" s="61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -14704,17 +14704,17 @@
       </c>
       <c r="C63" s="57" t="inlineStr">
         <is>
-          <t>5. Overburden Removal</t>
+          <t>1. Supporting Material Production and Transportation</t>
         </is>
       </c>
       <c r="D63" s="57" t="inlineStr">
         <is>
-          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+          <t>Ammonium nitrate {RoW}| market for ammonium nitrate | Cut-off, S</t>
         </is>
       </c>
       <c r="E63" s="57" t="inlineStr"/>
       <c r="F63" s="58" t="n">
-        <v>6.1744842</v>
+        <v>1.3259296</v>
       </c>
       <c r="G63" s="56" t="inlineStr">
         <is>
@@ -14722,14 +14722,14 @@
         </is>
       </c>
       <c r="H63" s="59" t="n">
-        <v>0.2551598752517306</v>
+        <v>0.07160300752919138</v>
       </c>
       <c r="I63" s="59" t="n">
-        <v>0.8520993870196539</v>
+        <v>0.8516655549430515</v>
       </c>
       <c r="J63" s="57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="J64" s="57" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="J65" s="65" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -14855,7 +14855,7 @@
       </c>
       <c r="J66" s="57" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="J67" s="65" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="J68" s="57" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="J69" s="65" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="J70" s="57" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="J71" s="57" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>241</t>
         </is>
       </c>
     </row>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="J72" s="61" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>204</t>
         </is>
       </c>
     </row>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="J73" s="65" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="J74" s="57" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>206</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="J75" s="65" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>278</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="J76" s="61" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>279</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="J77" s="57" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>280</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="J78" s="61" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>315</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="J79" s="65" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>316</t>
         </is>
       </c>
     </row>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="J80" s="57" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>317</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="J81" s="65" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>352</t>
         </is>
       </c>
     </row>
@@ -15527,7 +15527,7 @@
       </c>
       <c r="J82" s="61" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>353</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="J83" s="57" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
     </row>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="J84" s="61" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="J85" s="65" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>390</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="J86" s="57" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>391</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="J87" s="65" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>426</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="J88" s="57" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>427</t>
         </is>
       </c>
     </row>
@@ -15821,7 +15821,7 @@
       </c>
       <c r="J89" s="65" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>500</t>
         </is>
       </c>
     </row>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="J90" s="61" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>501</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="J91" s="57" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>502</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="J92" s="61" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>463</t>
         </is>
       </c>
     </row>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="J93" s="57" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>464</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="J94" s="61" t="inlineStr">
         <is>
-          <t>538, 575, 614</t>
+          <t>537, 574, 613</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="J95" s="57" t="inlineStr">
         <is>
-          <t>539, 576, 613</t>
+          <t>538, 575, 612</t>
         </is>
       </c>
     </row>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="J96" s="57" t="inlineStr">
         <is>
-          <t>649, 687, 725</t>
+          <t>648, 686, 724</t>
         </is>
       </c>
     </row>
